--- a/data/trans_dic/P25A$otro-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25A$otro-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, otros motivos</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, otros motivos (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,53</t>
+          <t>0,0; 8,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,4</t>
+          <t>0,0; 7,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,83; 36,42</t>
+          <t>18,7; 37,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,03; 51,3</t>
+          <t>5,68; 49,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,52</t>
+          <t>0,0; 16,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,72; 48,58</t>
+          <t>21,09; 49,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,19; 18,65</t>
+          <t>3,02; 18,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 8,56</t>
+          <t>0,87; 7,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,96; 39,01</t>
+          <t>22,56; 38,22</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,4</t>
+          <t>0,0; 5,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,18</t>
+          <t>0,77; 6,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,95; 39,6</t>
+          <t>7,77; 39,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,47</t>
+          <t>0,0; 8,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,07</t>
+          <t>0,0; 18,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 10,26</t>
+          <t>2,2; 10,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,05</t>
+          <t>0,55; 4,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,49</t>
+          <t>0,0; 5,99</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 13,32</t>
+          <t>1,59; 13,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,91</t>
+          <t>0,0; 5,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,13</t>
+          <t>0,0; 7,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,36</t>
+          <t>0,0; 48,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,3</t>
+          <t>0,0; 16,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,48</t>
+          <t>0,0; 16,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 13,63</t>
+          <t>2,51; 13,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,22</t>
+          <t>0,0; 6,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,06</t>
+          <t>0,0; 6,84</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,02</t>
+          <t>0,0; 11,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 13,03</t>
+          <t>1,85; 13,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,5; 34,84</t>
+          <t>15,93; 34,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,82</t>
+          <t>0,0; 14,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,55; 41,23</t>
+          <t>14,51; 40,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 9,61</t>
+          <t>1,43; 10,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 9,07</t>
+          <t>0,72; 8,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,7; 32,46</t>
+          <t>18,47; 33,54</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,66</t>
+          <t>0,0; 21,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,36</t>
+          <t>0,0; 25,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,48</t>
+          <t>0,0; 33,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,37</t>
+          <t>0,0; 9,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,59</t>
+          <t>0,0; 8,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,98</t>
+          <t>0,0; 12,65</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,92</t>
+          <t>0,0; 11,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,28</t>
+          <t>0,0; 7,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,17; 19,69</t>
+          <t>2,37; 21,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,18</t>
+          <t>0,0; 27,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,71</t>
+          <t>0,0; 38,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,03; 40,98</t>
+          <t>5,03; 40,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,34; 11,22</t>
+          <t>1,36; 11,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,92; 10,35</t>
+          <t>0,94; 10,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,53; 20,11</t>
+          <t>4,55; 19,81</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,49</t>
+          <t>0,0; 6,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,0; 3,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,29; 12,89</t>
+          <t>3,15; 12,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,9; 33,83</t>
+          <t>5,91; 32,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,15; 15,68</t>
+          <t>4,21; 16,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,4; 14,54</t>
+          <t>3,39; 15,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 11,37</t>
+          <t>2,36; 11,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,21</t>
+          <t>1,59; 6,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,22; 11,73</t>
+          <t>4,25; 11,85</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,78</t>
+          <t>0,0; 5,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,7</t>
+          <t>0,8; 7,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,11</t>
+          <t>0,0; 4,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,63; 15,58</t>
+          <t>2,59; 15,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,62</t>
+          <t>0,0; 11,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,35</t>
+          <t>0,0; 7,69</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,42; 6,55</t>
+          <t>1,5; 6,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,08; 6,48</t>
+          <t>1,08; 6,55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,98</t>
+          <t>0,0; 4,03</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,85</t>
+          <t>1,29; 3,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,57</t>
+          <t>1,19; 3,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,25; 12,09</t>
+          <t>7,13; 11,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,25; 15,29</t>
+          <t>7,57; 15,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,87; 7,42</t>
+          <t>3,17; 7,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,85; 17,24</t>
+          <t>9,39; 16,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,47</t>
+          <t>3,45; 6,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,28</t>
+          <t>2,11; 4,13</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,67; 12,91</t>
+          <t>8,8; 12,82</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, otros motivos</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, otros motivos (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4425</t>
+          <t>0; 3772</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6814</t>
+          <t>0; 6080</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14076; 28757</t>
+          <t>14763; 29875</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1611; 10298</t>
+          <t>1139; 9851</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6615</t>
+          <t>0; 6439</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11290; 25254</t>
+          <t>10964; 25635</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2125; 12409</t>
+          <t>2009; 12606</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1066; 10372</t>
+          <t>1057; 9518</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28755; 51074</t>
+          <t>29534; 50047</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7290</t>
+          <t>0; 6536</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 7479</t>
+          <t>932; 8243</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1924</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2056; 10239</t>
+          <t>2009; 10307</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5068</t>
+          <t>0; 5041</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4999</t>
+          <t>0; 5289</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3064; 14334</t>
+          <t>3073; 14010</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>973; 9127</t>
+          <t>997; 8992</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4567</t>
+          <t>0; 6083</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1026; 8491</t>
+          <t>1013; 8323</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4860</t>
+          <t>0; 4656</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5039</t>
+          <t>0; 4726</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5176</t>
+          <t>0; 6852</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4688</t>
+          <t>0; 5459</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4549</t>
+          <t>0; 4497</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1912; 10631</t>
+          <t>1957; 10462</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 7158</t>
+          <t>0; 7199</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6327</t>
+          <t>0; 6127</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 9124</t>
+          <t>0; 8499</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1981; 13739</t>
+          <t>1954; 14369</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14367; 30342</t>
+          <t>13874; 30074</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5583</t>
+          <t>0; 5542</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1891</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6054; 18416</t>
+          <t>6483; 18195</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>967; 10911</t>
+          <t>1621; 11388</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1089; 13787</t>
+          <t>1095; 13596</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23322; 42763</t>
+          <t>24340; 44190</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1916</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2142</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1834</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 6578</t>
+          <t>0; 6158</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6540</t>
+          <t>0; 6980</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 5550</t>
+          <t>0; 5698</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 7276</t>
+          <t>0; 6310</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 6642</t>
+          <t>0; 6582</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 7314</t>
+          <t>0; 6176</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6832</t>
+          <t>0; 6210</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5223</t>
+          <t>0; 6363</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>962; 8739</t>
+          <t>1050; 9462</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 5114</t>
+          <t>0; 5149</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 8021</t>
+          <t>0; 8512</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>846; 6885</t>
+          <t>846; 6754</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>961; 8044</t>
+          <t>972; 8170</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>970; 10862</t>
+          <t>988; 10680</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2769; 12304</t>
+          <t>2783; 12119</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5979</t>
+          <t>0; 5674</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4058</t>
+          <t>0; 5319</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4182; 16354</t>
+          <t>4002; 15664</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1941; 11119</t>
+          <t>1942; 10547</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3808; 14402</t>
+          <t>3861; 15371</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2873; 12275</t>
+          <t>2860; 13286</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2868; 14215</t>
+          <t>2951; 13868</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3957; 15785</t>
+          <t>4045; 15679</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8918; 24798</t>
+          <t>8985; 25040</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 6621</t>
+          <t>0; 7455</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1032; 8721</t>
+          <t>1042; 9307</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 5213</t>
+          <t>0; 5037</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1899; 11248</t>
+          <t>1872; 11246</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 6441</t>
+          <t>0; 7490</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 5339</t>
+          <t>0; 4920</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3002; 13808</t>
+          <t>3162; 14091</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2123; 12772</t>
+          <t>2129; 12912</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 6612</t>
+          <t>0; 6689</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>8406; 24022</t>
+          <t>8086; 24256</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>10634; 29115</t>
+          <t>9690; 27799</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>43893; 73216</t>
+          <t>43197; 71994</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18170; 38337</t>
+          <t>18981; 39836</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>11097; 28684</t>
+          <t>12242; 29632</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>33090; 57877</t>
+          <t>31537; 56648</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30420; 56623</t>
+          <t>30197; 55524</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>25667; 51431</t>
+          <t>25339; 49613</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>81630; 121487</t>
+          <t>82874; 120653</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$otro-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25A$otro-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,12</t>
+          <t>0,0; 7,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,5</t>
+          <t>0,0; 8,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,7; 37,84</t>
+          <t>18,08; 37,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,68; 49,08</t>
+          <t>5,74; 52,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,08</t>
+          <t>0,0; 16,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,09; 49,32</t>
+          <t>21,98; 49,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 18,95</t>
+          <t>3,25; 18,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 7,86</t>
+          <t>0,84; 7,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,56; 38,22</t>
+          <t>22,13; 38,69</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,74</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,82</t>
+          <t>0,78; 7,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,32 +803,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,77; 39,87</t>
+          <t>7,8; 39,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,43</t>
+          <t>0,0; 8,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,06</t>
+          <t>0,0; 17,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 10,03</t>
+          <t>2,19; 10,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,97</t>
+          <t>0,55; 5,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,99</t>
+          <t>0,0; 5,51</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 13,06</t>
+          <t>1,6; 13,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,66</t>
+          <t>0,0; 6,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,62</t>
+          <t>0,0; 7,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,13</t>
+          <t>0,0; 42,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,65</t>
+          <t>0,0; 19,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,29</t>
+          <t>0,0; 13,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 13,42</t>
+          <t>2,52; 14,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,26</t>
+          <t>0,0; 6,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,84</t>
+          <t>0,0; 6,2</t>
         </is>
       </c>
     </row>
@@ -1008,22 +1008,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,2</t>
+          <t>0,0; 10,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 13,63</t>
+          <t>1,05; 12,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,93; 34,53</t>
+          <t>15,42; 33,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,71</t>
+          <t>0,0; 14,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,51; 40,74</t>
+          <t>13,72; 39,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 10,03</t>
+          <t>0,84; 9,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 8,95</t>
+          <t>0,72; 8,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,47; 33,54</t>
+          <t>18,02; 32,61</t>
         </is>
       </c>
     </row>
@@ -1133,32 +1133,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,22</t>
+          <t>0,0; 21,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,99</t>
+          <t>0,0; 25,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,35</t>
+          <t>0,0; 39,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,0</t>
+          <t>0,0; 8,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,52</t>
+          <t>0,0; 8,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,65</t>
+          <t>0,0; 14,91</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,75</t>
+          <t>0,0; 11,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,66</t>
+          <t>0,0; 4,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,37; 21,32</t>
+          <t>2,19; 19,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,37</t>
+          <t>0,0; 21,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,96</t>
+          <t>0,0; 38,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,03; 40,2</t>
+          <t>5,21; 39,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,36; 11,4</t>
+          <t>1,36; 11,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 10,18</t>
+          <t>0,94; 11,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,55; 19,81</t>
+          <t>4,47; 21,3</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,16</t>
+          <t>0,0; 6,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,27</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,15; 12,34</t>
+          <t>3,33; 12,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,91; 32,09</t>
+          <t>5,76; 31,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,21; 16,74</t>
+          <t>4,23; 16,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,39; 15,73</t>
+          <t>3,46; 16,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,36; 11,09</t>
+          <t>2,67; 10,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,16</t>
+          <t>1,58; 6,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,25; 11,85</t>
+          <t>4,34; 11,39</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,38</t>
+          <t>0,0; 5,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,15</t>
+          <t>0,79; 7,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,93</t>
+          <t>0,0; 5,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,59; 15,58</t>
+          <t>2,66; 15,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,19</t>
+          <t>0,0; 9,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,69</t>
+          <t>0,0; 6,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,5; 6,69</t>
+          <t>1,58; 6,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,08; 6,55</t>
+          <t>1,07; 6,11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,03</t>
+          <t>0,0; 3,7</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,88</t>
+          <t>1,31; 3,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,41</t>
+          <t>1,1; 3,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,13; 11,89</t>
+          <t>7,27; 12,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,57; 15,89</t>
+          <t>7,47; 15,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,67</t>
+          <t>2,91; 7,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,39; 16,87</t>
+          <t>9,14; 16,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,34</t>
+          <t>3,52; 6,37</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,13</t>
+          <t>2,07; 4,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,8; 12,82</t>
+          <t>8,68; 12,7</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3772</t>
+          <t>0; 3391</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6080</t>
+          <t>0; 6832</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14763; 29875</t>
+          <t>14275; 29709</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1139; 9851</t>
+          <t>1153; 10613</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6439</t>
+          <t>0; 6744</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10964; 25635</t>
+          <t>11423; 25588</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2009; 12606</t>
+          <t>2159; 12316</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1057; 9518</t>
+          <t>1021; 9550</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29534; 50047</t>
+          <t>28980; 50662</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6536</t>
+          <t>0; 6311</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>932; 8243</t>
+          <t>940; 8543</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2039,32 +2039,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2009; 10307</t>
+          <t>2016; 10330</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5041</t>
+          <t>0; 5107</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5289</t>
+          <t>0; 5064</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3073; 14010</t>
+          <t>3064; 14175</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>997; 8992</t>
+          <t>1003; 10069</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6083</t>
+          <t>0; 5599</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1013; 8323</t>
+          <t>1023; 8542</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4656</t>
+          <t>0; 5631</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4726</t>
+          <t>0; 4750</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 6852</t>
+          <t>0; 6074</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5459</t>
+          <t>0; 6430</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4497</t>
+          <t>0; 3669</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1957; 10462</t>
+          <t>1968; 10943</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 7199</t>
+          <t>0; 7013</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6127</t>
+          <t>0; 5552</t>
         </is>
       </c>
     </row>
@@ -2350,22 +2350,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 8499</t>
+          <t>0; 8243</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1954; 14369</t>
+          <t>1109; 13273</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13874; 30074</t>
+          <t>13430; 29180</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5542</t>
+          <t>0; 5589</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2375,22 +2375,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6483; 18195</t>
+          <t>6128; 17810</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1621; 11388</t>
+          <t>957; 10393</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1095; 13596</t>
+          <t>1090; 13416</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24340; 44190</t>
+          <t>23738; 42960</t>
         </is>
       </c>
     </row>
@@ -2528,32 +2528,32 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 6158</t>
+          <t>0; 6137</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6980</t>
+          <t>0; 6781</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 5698</t>
+          <t>0; 6800</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6310</t>
+          <t>0; 6100</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 6582</t>
+          <t>0; 6786</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 6176</t>
+          <t>0; 7277</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6210</t>
+          <t>0; 6263</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6363</t>
+          <t>0; 3940</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1050; 9462</t>
+          <t>972; 8644</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 5149</t>
+          <t>0; 4134</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 8512</t>
+          <t>0; 8494</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>846; 6754</t>
+          <t>875; 6674</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>972; 8170</t>
+          <t>976; 8106</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>988; 10680</t>
+          <t>986; 11609</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2783; 12119</t>
+          <t>2735; 13030</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5674</t>
+          <t>0; 5857</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 5319</t>
+          <t>0; 4091</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4002; 15664</t>
+          <t>4228; 16162</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1942; 10547</t>
+          <t>1894; 10331</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3861; 15371</t>
+          <t>3884; 14812</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2860; 13286</t>
+          <t>2920; 14097</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2951; 13868</t>
+          <t>3336; 13692</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4045; 15679</t>
+          <t>4017; 15771</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8985; 25040</t>
+          <t>9165; 24081</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 7455</t>
+          <t>0; 7136</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1042; 9307</t>
+          <t>1033; 9803</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 5037</t>
+          <t>0; 6091</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1872; 11246</t>
+          <t>1922; 11480</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 7490</t>
+          <t>0; 6302</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 4920</t>
+          <t>0; 3928</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3162; 14091</t>
+          <t>3326; 14392</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2129; 12912</t>
+          <t>2106; 12038</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 6689</t>
+          <t>0; 6136</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>8086; 24256</t>
+          <t>8171; 23471</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9690; 27799</t>
+          <t>8965; 27330</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>43197; 71994</t>
+          <t>44049; 73170</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18981; 39836</t>
+          <t>18728; 38528</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>12242; 29632</t>
+          <t>11235; 29119</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>31537; 56648</t>
+          <t>30698; 57047</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30197; 55524</t>
+          <t>30810; 55759</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>25339; 49613</t>
+          <t>24869; 48291</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>82874; 120653</t>
+          <t>81718; 119585</t>
         </is>
       </c>
     </row>
